--- a/reports/module-migration-sunset-backlog/2026-07-27/CANONICAL_PROMOTION_IMPLEMENTATION_MATRIX.xlsx
+++ b/reports/module-migration-sunset-backlog/2026-07-27/CANONICAL_PROMOTION_IMPLEMENTATION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion Matrix" sheetId="1" r:id="R52109befb1494a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion Matrix" sheetId="1" r:id="Ra7c374ff0f804aa2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -321,6 +321,7 @@
     <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="42" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="42" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -331,36 +332,39 @@
         <x:v>schema_table</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>canonical_target</x:v>
+        <x:v>provisional_canonical_object_family</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
+        <x:v>mapping_confidence</x:v>
+      </x:c>
+      <x:c r="E1" s="9" t="str">
         <x:v>current_authority</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>identity_map_required</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>publication_trigger</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>required_evidence</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>historical_backfill</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>dual_run_requirement</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="K1" s="9" t="str">
         <x:v>reconciliation_rule</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="L1" s="9" t="str">
         <x:v>cutover_dependency</x:v>
       </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="M1" s="9" t="str">
         <x:v>rollback_path</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="N1" s="9" t="str">
         <x:v>status</x:v>
       </x:c>
     </x:row>
@@ -375,33 +379,36 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
         <x:v>source_id; evidence_type; confidence_level; evidence_payload</x:v>
       </x:c>
-      <x:c r="H2" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I2" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J2" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K2" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L2" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M2" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N2" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -416,33 +423,36 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F3" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="str">
         <x:v>source_id; source_name; source_date; source_owner; source_status; lineage; source_payload</x:v>
       </x:c>
-      <x:c r="H3" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I3" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J3" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K3" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L3" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M3" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N3" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -457,33 +467,36 @@
         <x:v>knowledge.evidence_chunk</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="str">
         <x:v>artifact_id; source_event_id; provenance; confidence</x:v>
       </x:c>
-      <x:c r="H4" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I4" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J4" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K4" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L4" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M4" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N4" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -498,33 +511,36 @@
         <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="str">
         <x:v>artifact_id; source_event_id; provenance; confidence</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J5" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K5" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L5" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M5" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N5" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -536,36 +552,39 @@
         <x:v>public.source_contract_evidence_manifests</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.evidence_manifest</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="str">
         <x:v>source_event_id; source_artifact_id; evidence_pack_name; source_type</x:v>
       </x:c>
-      <x:c r="H6" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I6" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J6" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K6" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L6" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M6" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N6" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -577,36 +596,39 @@
         <x:v>public.source_contract_evidence_metrics</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
         <x:v>source_event_id; evidence_family; confidence</x:v>
       </x:c>
-      <x:c r="H7" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I7" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J7" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K7" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L7" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M7" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N7" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -618,36 +640,39 @@
         <x:v>public.source_contract_evidence_rows</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.evidence_fragment_or_contract_fact_assertion</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G8" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
         <x:v>source_event_id; source_artifact_id; evidence_family; source_sheet; source_row_number; confidence</x:v>
       </x:c>
-      <x:c r="H8" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I8" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J8" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K8" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L8" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M8" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N8" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -659,36 +684,39 @@
         <x:v>public.source_contract_optimization_findings</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.contract_finding</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
         <x:v>source_event_id; confidence; evidence_refs</x:v>
       </x:c>
-      <x:c r="H9" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I9" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J9" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K9" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L9" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M9" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N9" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -700,36 +728,39 @@
         <x:v>public.source_contract_optimization_levers</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.value_driver_or_commercial_lever</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
         <x:v>source_event_id</x:v>
       </x:c>
-      <x:c r="H10" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I10" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J10" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K10" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L10" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M10" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N10" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -741,36 +772,39 @@
         <x:v>public.source_contract_optimization_profiles</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.contract_profile</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="str">
         <x:v>source_event_id; source_type; evidence_artifact_ids; evidence_refs</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I11" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J11" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K11" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L11" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M11" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N11" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -785,33 +819,36 @@
         <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E12" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F12" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G12" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="str">
         <x:v>source_event_id; source_method; source_citation; confidence</x:v>
       </x:c>
-      <x:c r="H12" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I12" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J12" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K12" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L12" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M12" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N12" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -823,36 +860,39 @@
         <x:v>public.source_meeting_outcomes</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="str">
         <x:v>artifact_id; source_event_id; provenance; confidence</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I13" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J13" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K13" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L13" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M13" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N13" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -864,36 +904,39 @@
         <x:v>public.source_value_chain</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_flow_step</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="str">
         <x:v>source_event_id</x:v>
       </x:c>
-      <x:c r="H14" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I14" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J14" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K14" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L14" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M14" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N14" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -905,36 +948,39 @@
         <x:v>public.source_value_levers</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_driver_or_lever</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="str">
         <x:v>source_event_id; confidence; evidence_refs; insufficient_evidence; missing_evidence</x:v>
       </x:c>
-      <x:c r="H15" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I15" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J15" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K15" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L15" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M15" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N15" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -946,36 +992,39 @@
         <x:v>public.source_value_lines</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E16" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F16" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G16" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="str">
         <x:v>evidence_artifact_id</x:v>
       </x:c>
-      <x:c r="H16" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I16" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J16" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K16" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L16" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M16" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N16" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -987,36 +1036,39 @@
         <x:v>public.source_value_states</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_state_or_readiness</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H17" s="5" t="str">
         <x:v>source_event_id; evidence_ledger_ids</x:v>
       </x:c>
-      <x:c r="H17" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I17" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J17" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K17" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L17" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M17" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N17" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1028,36 +1080,39 @@
         <x:v>public.source_vendor_commitments</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.commercial_commitment</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H18" s="5" t="str">
         <x:v>artifact_id; source_event_id; provenance; confidence</x:v>
       </x:c>
-      <x:c r="H18" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I18" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J18" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K18" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L18" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M18" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N18" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1069,36 +1124,39 @@
         <x:v>public.source_vendor_proposal_facts</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.proposal_fact_assertion</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="str">
         <x:v>source_event_id; proposal_artifact_id; source_quote; source_pointer; confidence</x:v>
       </x:c>
-      <x:c r="H19" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I19" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J19" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K19" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L19" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M19" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N19" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1110,36 +1168,39 @@
         <x:v>public.vendor_contracts</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="str">
         <x:v>No parsed lineage fields; inspect write path before promotion</x:v>
       </x:c>
-      <x:c r="H20" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I20" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J20" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K20" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L20" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M20" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N20" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1154,33 +1215,36 @@
         <x:v>knowledge.metric_definition</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H21" s="5" t="str">
         <x:v>artifact_default</x:v>
       </x:c>
-      <x:c r="H21" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I21" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J21" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K21" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L21" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M21" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N21" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1192,36 +1256,39 @@
         <x:v>cio_tower.tool_identity_aliases</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D22" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E22" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F22" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G22" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H22" s="5" t="str">
         <x:v>source</x:v>
       </x:c>
-      <x:c r="H22" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I22" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J22" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K22" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L22" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M22" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N22" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1233,36 +1300,39 @@
         <x:v>public.ai_control_actions</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.action_or_decision</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="str">
         <x:v>evidence_state</x:v>
       </x:c>
-      <x:c r="H23" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I23" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J23" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K23" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L23" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M23" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N23" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1274,36 +1344,39 @@
         <x:v>public.ai_control_agent_outcomes</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.outcome</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G24" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H24" s="5" t="str">
         <x:v>source_id; evidence_state</x:v>
       </x:c>
-      <x:c r="H24" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I24" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J24" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K24" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L24" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M24" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N24" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1315,36 +1388,39 @@
         <x:v>public.ai_control_benefit_realization</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H25" s="5" t="str">
         <x:v>source_id; confidence; evidence_state</x:v>
       </x:c>
-      <x:c r="H25" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I25" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J25" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K25" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L25" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M25" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N25" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1356,36 +1432,39 @@
         <x:v>public.ai_control_context_facts</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.fact_assertion</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G26" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H26" s="5" t="str">
         <x:v>confidence; evidence_state; evidence_keys</x:v>
       </x:c>
-      <x:c r="H26" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I26" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J26" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K26" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L26" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M26" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N26" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1397,36 +1476,39 @@
         <x:v>public.ai_control_context_relationships</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.relationship_assertion</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E27" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F27" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G27" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H27" s="5" t="str">
         <x:v>No parsed lineage fields; inspect write path before promotion</x:v>
       </x:c>
-      <x:c r="H27" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I27" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J27" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K27" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L27" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M27" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N27" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1438,36 +1520,39 @@
         <x:v>public.ai_control_dora_metrics</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H28" s="5" t="str">
         <x:v>source_id; evidence_state</x:v>
       </x:c>
-      <x:c r="H28" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I28" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J28" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K28" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L28" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M28" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N28" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1479,36 +1564,39 @@
         <x:v>public.ai_control_evidence_items</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H29" s="5" t="str">
         <x:v>evidence_key; evidence_type; citation_label; citation_locator; evidence_pointer; evidence_state; confidence</x:v>
       </x:c>
-      <x:c r="H29" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I29" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J29" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K29" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L29" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M29" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N29" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1523,33 +1611,36 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H30" s="5" t="str">
         <x:v>source_id</x:v>
       </x:c>
-      <x:c r="H30" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I30" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J30" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K30" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L30" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M30" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N30" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1561,36 +1652,39 @@
         <x:v>public.ai_control_persona_productivity</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E31" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F31" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G31" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="str">
         <x:v>source_id; confidence; evidence_state</x:v>
       </x:c>
-      <x:c r="H31" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I31" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J31" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K31" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L31" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M31" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N31" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1605,33 +1699,36 @@
         <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E32" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F32" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G32" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H32" s="5" t="str">
         <x:v>source_id; evidence_state</x:v>
       </x:c>
-      <x:c r="H32" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I32" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J32" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K32" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L32" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M32" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N32" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1646,33 +1743,36 @@
         <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E33" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F33" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G33" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H33" s="5" t="str">
         <x:v>source_id; evidence_state</x:v>
       </x:c>
-      <x:c r="H33" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I33" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J33" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K33" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L33" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M33" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N33" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1684,36 +1784,39 @@
         <x:v>public.ai_control_tool_usage_monthly</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E34" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F34" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G34" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H34" s="5" t="str">
         <x:v>source_id; evidence_state</x:v>
       </x:c>
-      <x:c r="H34" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I34" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J34" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K34" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L34" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M34" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N34" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1728,33 +1831,36 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E35" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F35" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G35" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H35" s="5" t="str">
         <x:v>No parsed lineage fields; inspect write path before promotion</x:v>
       </x:c>
-      <x:c r="H35" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I35" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J35" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K35" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L35" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M35" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N35" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1766,36 +1872,39 @@
         <x:v>public.enterprise_context_records</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E36" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F36" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G36" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H36" s="5" t="str">
         <x:v>source_id; source_file_id; source_system; source_record_id; source_file; source_sheet; source_row_number; confidence; evidence_pointer</x:v>
       </x:c>
-      <x:c r="H36" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I36" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J36" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K36" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L36" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M36" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N36" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1810,33 +1919,36 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E37" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F37" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G37" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H37" s="5" t="str">
         <x:v>source_system</x:v>
       </x:c>
-      <x:c r="H37" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I37" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J37" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K37" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L37" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M37" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N37" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1851,33 +1963,36 @@
         <x:v>knowledge.vendor</x:v>
       </x:c>
       <x:c r="D38" s="5" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E38" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F38" s="5" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G38" s="5" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H38" s="5" t="str">
         <x:v>evidence_ids; citations; lineage</x:v>
       </x:c>
-      <x:c r="H38" s="5" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I38" s="5" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J38" s="5" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K38" s="5" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L38" s="5" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M38" s="5" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N38" s="5" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
@@ -1892,33 +2007,36 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="D39" s="6" t="str">
-        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E39" s="6" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Candidate/domain-derived; not canonical until promoted</x:v>
       </x:c>
       <x:c r="F39" s="6" t="str">
-        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G39" s="6" t="str">
+        <x:v>accepted/reviewed/published row state plus tenant and lineage validation</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str">
         <x:v>source; source_engagement_id; source_file_id</x:v>
       </x:c>
-      <x:c r="H39" s="6" t="str">
-        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
-      </x:c>
       <x:c r="I39" s="6" t="str">
-        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
+        <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
       <x:c r="J39" s="6" t="str">
-        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
+        <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
       <x:c r="K39" s="6" t="str">
-        <x:v>Healthcare publication/consumption framework certified first</x:v>
+        <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
       <x:c r="L39" s="6" t="str">
-        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+        <x:v>Healthcare publication/consumption framework certified first</x:v>
       </x:c>
       <x:c r="M39" s="6" t="str">
+        <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
+      </x:c>
+      <x:c r="N39" s="6" t="str">
         <x:v>candidate_not_authorized</x:v>
       </x:c>
     </x:row>
